--- a/model_templates/ark.BulkATAC-seqAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.BulkATAC-seqAssayMetadataTemplate.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -20072,7 +20072,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="177">
   <si>
     <t>Component</t>
   </si>
@@ -20170,6 +20170,9 @@
     <t>CITESeq</t>
   </si>
   <si>
+    <t>unknown</t>
+  </si>
+  <si>
     <t>10x Chromium GEM-X Single Cell 5' v3</t>
   </si>
   <si>
@@ -20179,7 +20182,7 @@
     <t>BD FACSCanto</t>
   </si>
   <si>
-    <t>modified GRCh38</t>
+    <t>GRCh38</t>
   </si>
   <si>
     <t>Cell Ranger ATAC v1.1.0</t>
@@ -20200,7 +20203,7 @@
     <t>BD FACSCanto II</t>
   </si>
   <si>
-    <t>unknown</t>
+    <t>modified GRCh38</t>
   </si>
   <si>
     <t>Cell Ranger v3.0.0</t>
@@ -20221,9 +20224,6 @@
     <t>BD FACSDiscover A8</t>
   </si>
   <si>
-    <t>vdj_GRCh38_alts_ensembl-4.0.0</t>
-  </si>
-  <si>
     <t>Cell Ranger v3.0.1</t>
   </si>
   <si>
@@ -20240,6 +20240,9 @@
   </si>
   <si>
     <t>BD FACSDiscover S8</t>
+  </si>
+  <si>
+    <t>vdj_GRCh38_alts_ensembl-4.0.0</t>
   </si>
   <si>
     <t>Cell Ranger v3.0.2</t>
@@ -20323,7 +20326,7 @@
     <t>kiloplex</t>
   </si>
   <si>
-    <t>10x GEM-X Universal 5? Gene Expression v3</t>
+    <t>10x GEM-X Universal 5' Gene Expression v3</t>
   </si>
   <si>
     <t>Tn5-accessible gDNA</t>
@@ -20587,6 +20590,9 @@
     <t>Sony MA900</t>
   </si>
   <si>
+    <t>Spatial Genomics Gene Positioning System</t>
+  </si>
+  <si>
     <t>Thermo Fisher Attune CytPix</t>
   </si>
   <si>
@@ -20709,6 +20715,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -47976,17 +47986,17 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="D2:D1000">
       <formula1>Sheet2!$D$2:$D$32</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="C2:C1000">
+      <formula1>Sheet2!$C$2:$C$4</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="K2:K1000">
       <formula1>Sheet2!$K$2:$K$31</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="C2:C1000">
-      <formula1>Sheet2!$C$2:$C$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
+      <formula1>Sheet2!$J$2:$J$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="L2:L1000">
       <formula1>Sheet2!$L$2:$L$6</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
-      <formula1>Sheet2!$J$2:$J$6</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -48101,63 +48111,66 @@
       <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>37</v>
       </c>
+      <c r="L4" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>50</v>
@@ -48179,442 +48192,450 @@
       <c r="G7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>56</v>
       </c>
+      <c r="K7" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36">
       <c r="G36" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37">
       <c r="G37" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38">
       <c r="G38" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39">
       <c r="G39" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40">
       <c r="G40" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41">
       <c r="G41" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42">
       <c r="G42" s="7" t="s">
-        <v>42</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43">
       <c r="G43" s="7" t="s">
-        <v>174</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44">
       <c r="G44" s="7" t="s">
-        <v>166</v>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="G45" s="7" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/model_templates/ark.BulkATAC-seqAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.BulkATAC-seqAssayMetadataTemplate.xlsx
@@ -20072,7 +20072,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="176">
   <si>
     <t>Component</t>
   </si>
@@ -20590,9 +20590,6 @@
     <t>Sony MA900</t>
   </si>
   <si>
-    <t>Spatial Genomics Gene Positioning System</t>
-  </si>
-  <si>
     <t>Thermo Fisher Attune CytPix</t>
   </si>
   <si>
@@ -48620,21 +48617,16 @@
     </row>
     <row r="42">
       <c r="G42" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="G43" s="7" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="43">
-      <c r="G43" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
     <row r="44">
       <c r="G44" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="G45" s="7" t="s">
         <v>167</v>
       </c>
     </row>

--- a/model_templates/ark.BulkATAC-seqAssayMetadataTemplate.xlsx
+++ b/model_templates/ark.BulkATAC-seqAssayMetadataTemplate.xlsx
@@ -47969,14 +47969,14 @@
       <formula>$D1 = "10x GEM-X Flex Gene Expression Human"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1:M1000">
+  <conditionalFormatting sqref="N1:N1000">
     <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>$C1 = "single specimen"</formula>
+      <formula>$C1 = "multispecimen"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1:N1000">
+  <conditionalFormatting sqref="M1:M1000">
     <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$C1 = "multispecimen"</formula>
+      <formula>$C1 = "single specimen"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
